--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260615.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.16%</t>
+          <t>18.44%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.60%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>5.09%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.70%</t>
         </is>
       </c>
     </row>
@@ -704,117 +704,117 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.28%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>12,101,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>1,350,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,350,000</t>
+          <t>4,700,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,700,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,280,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -836,29 +836,29 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>8,900,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,900,000</t>
+          <t>6,020,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,090,000</t>
+          <t>16,350,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>16,350,000</t>
+          <t>1,090,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>279,000</t>
+          <t>430,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>840,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>430,000</t>
+          <t>840,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1166,95 +1166,95 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,497,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>1,710,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,44 +1305,44 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>680,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,710,000</t>
+          <t>680,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1452,29 +1452,29 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1518,139 +1518,139 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>957,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>916,000</t>
+          <t>957,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>748,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>7,442,604,797</t>
+          <t>7,181,430,219</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-2,292,205,803</t>
+          <t>-1,017,978,273</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
